--- a/notes/gear_ratios.xlsx
+++ b/notes/gear_ratios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github_projects\spider_dropper\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BF2591-2923-43B4-9D94-3F1B1FFCC22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9C677B-5A43-418F-A8F0-B9A50B7360A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{E034330B-BFBD-48DE-B9DD-948610082F57}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{E034330B-BFBD-48DE-B9DD-948610082F57}"/>
   </bookViews>
   <sheets>
     <sheet name="Ratios" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>ISO module</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>Ratio of Diameters</t>
+  </si>
+  <si>
+    <t>(includes max extent of head of set screw)</t>
   </si>
 </sst>
 </file>
@@ -173,6 +176,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -181,9 +187,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -266,10 +269,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Ratios!$C$10:$C$51</c:f>
+              <c:f>Ratios!$C$10:$C$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>57</c:v>
                 </c:pt>
@@ -346,13 +349,13 @@
                   <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>57</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>58</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>59</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>61</c:v>
@@ -361,40 +364,58 @@
                   <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>62</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>63</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>64</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>66</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>67</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>68</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>69</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>70</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>71</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>73</c:v>
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>79</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -426,10 +447,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Ratios!$G$10:$G$51</c:f>
+              <c:f>Ratios!$G$10:$G$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>139</c:v>
                 </c:pt>
@@ -554,6 +575,24 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="41">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
@@ -586,10 +625,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Ratios!$F$10:$F$51</c:f>
+              <c:f>Ratios!$F$10:$F$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>88.5</c:v>
                 </c:pt>
@@ -666,13 +705,13 @@
                   <c:v>88.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>88.5</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>90</c:v>
+                  <c:v>91.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>91.5</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>94.5</c:v>
@@ -681,40 +720,58 @@
                   <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>96</c:v>
+                  <c:v>97.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>97.5</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>99</c:v>
+                  <c:v>100.5</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>102</c:v>
+                  <c:v>103.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>103.5</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>105</c:v>
+                  <c:v>106.5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>106.5</c:v>
+                  <c:v>108</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>108</c:v>
+                  <c:v>109.5</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>109.5</c:v>
+                  <c:v>111</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>112.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>112.5</c:v>
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>115.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>118.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>118.5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>121.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -746,10 +803,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Ratios!$M$10:$M$51</c:f>
+              <c:f>Ratios!$M$10:$M$57</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>26.430975742619378</c:v>
                 </c:pt>
@@ -826,10 +883,10 @@
                   <c:v>89.48714732190075</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>92.826633214776791</c:v>
+                  <c:v>90.979258039994278</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>94.247691041532534</c:v>
+                  <c:v>92.409197478167272</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>95.609538125506802</c:v>
@@ -841,10 +898,10 @@
                   <c:v>98.169810643378426</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>101.24213766482437</c:v>
+                  <c:v>99.374644769435676</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>102.38673008457876</c:v>
+                  <c:v>100.53313912141377</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>103.48729971895794</c:v>
@@ -853,28 +910,46 @@
                   <c:v>104.54633842373795</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>107.44476014208318</c:v>
+                  <c:v>105.56615347278535</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>108.41090071486492</c:v>
+                  <c:v>106.54888433823102</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>109.34190890318186</c:v>
+                  <c:v>107.49651767276791</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>110.23966679905892</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>112.98281592534995</c:v>
+                  <c:v>111.10592441788768</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>113.80094812091045</c:v>
+                  <c:v>113.94231108434302</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>114.75034566041005</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>117.35401262773713</c:v>
+                  <c:v>115.53144575060817</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>118.0917182684798</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>118.80523683903417</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>119.49573868150618</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>121.9734217633174</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>122.6026746094917</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>123.21226330422303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1981,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1AACE9-797C-4CC1-8EA8-81631CAC12B7}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.765625" customWidth="1"/>
@@ -2049,10 +2124,13 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>21.8</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -2067,31 +2145,31 @@
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
       <c r="J8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="10"/>
       <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
@@ -2187,7 +2265,7 @@
         <f t="shared" ref="M10:M51" si="9">L10 + 4*$C$6*_xlfn.CEILING.MATH(K10)</f>
         <v>26.430975742619378</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="7">
         <f>F10/M10</f>
         <v>3.3483440362474268</v>
       </c>
@@ -2242,7 +2320,7 @@
         <f t="shared" si="9"/>
         <v>26.606738158033906</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="7">
         <f t="shared" ref="N11:N51" si="10">F11/M11</f>
         <v>3.3262250890862179</v>
       </c>
@@ -2297,7 +2375,7 @@
         <f t="shared" si="9"/>
         <v>26.782500573448431</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="7">
         <f t="shared" si="10"/>
         <v>3.3043964568318507</v>
       </c>
@@ -2352,7 +2430,7 @@
         <f t="shared" si="9"/>
         <v>28.606738158033906</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="7">
         <f t="shared" si="10"/>
         <v>3.0936767243820036</v>
       </c>
@@ -2407,7 +2485,7 @@
         <f t="shared" si="9"/>
         <v>28.606738158033906</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="7">
         <f t="shared" si="10"/>
         <v>3.0936767243820036</v>
       </c>
@@ -2462,7 +2540,7 @@
         <f t="shared" si="9"/>
         <v>29.309787819692012</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="7">
         <f t="shared" si="10"/>
         <v>3.0194691460898455</v>
       </c>
@@ -2517,7 +2595,7 @@
         <f t="shared" si="9"/>
         <v>30.606738158033906</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="7">
         <f t="shared" si="10"/>
         <v>2.891520146414877</v>
       </c>
@@ -2546,7 +2624,7 @@
         <v>88.5</v>
       </c>
       <c r="G17">
-        <f t="shared" ref="G17:G51" si="11">_xlfn.CEILING.MATH(($C$4 + 2*(1+$C$2)*$C$1) / $C$1)</f>
+        <f t="shared" ref="G17:G57" si="11">_xlfn.CEILING.MATH(($C$4 + 2*(1+$C$2)*$C$1) / $C$1)</f>
         <v>19</v>
       </c>
       <c r="H17">
@@ -2573,7 +2651,7 @@
         <f t="shared" si="9"/>
         <v>32.715887143008239</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="7">
         <f t="shared" si="10"/>
         <v>2.7051077543197071</v>
       </c>
@@ -2629,7 +2707,7 @@
         <f t="shared" si="9"/>
         <v>36.055373035884273</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="7">
         <f t="shared" si="10"/>
         <v>2.4545578799564765</v>
       </c>
@@ -2685,7 +2763,7 @@
         <f t="shared" si="9"/>
         <v>39.3948589287603</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="7">
         <f t="shared" si="10"/>
         <v>2.2464860239768591</v>
       </c>
@@ -2741,7 +2819,7 @@
         <f t="shared" si="9"/>
         <v>42.734344821636327</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="7">
         <f t="shared" si="10"/>
         <v>2.070933820779969</v>
       </c>
@@ -2797,7 +2875,7 @@
         <f t="shared" si="9"/>
         <v>46.073830714512354</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="7">
         <f t="shared" si="10"/>
         <v>1.9208300813616574</v>
       </c>
@@ -2853,7 +2931,7 @@
         <f t="shared" si="9"/>
         <v>49.413316607388396</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="7">
         <f t="shared" si="10"/>
         <v>1.7910151772076612</v>
       </c>
@@ -2909,7 +2987,7 @@
         <f t="shared" si="9"/>
         <v>52.752802500264416</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="7">
         <f t="shared" si="10"/>
         <v>1.6776359890937815</v>
       </c>
@@ -2965,7 +3043,7 @@
         <f t="shared" si="9"/>
         <v>56.092288393140457</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="7">
         <f t="shared" si="10"/>
         <v>1.5777569882640532</v>
       </c>
@@ -3021,7 +3099,7 @@
         <f t="shared" si="9"/>
         <v>59.431774286016477</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="7">
         <f t="shared" si="10"/>
         <v>1.4891024382696731</v>
       </c>
@@ -3077,7 +3155,7 @@
         <f t="shared" si="9"/>
         <v>62.771260178892504</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="7">
         <f t="shared" si="10"/>
         <v>1.4098808873325608</v>
       </c>
@@ -3133,7 +3211,7 @@
         <f t="shared" si="9"/>
         <v>66.110746071768546</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="7">
         <f t="shared" si="10"/>
         <v>1.338662853750374</v>
       </c>
@@ -3189,7 +3267,7 @@
         <f t="shared" si="9"/>
         <v>69.450231964644559</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="7">
         <f t="shared" si="10"/>
         <v>1.2742937999840407</v>
       </c>
@@ -3245,7 +3323,7 @@
         <f t="shared" si="9"/>
         <v>72.7897178575206</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="7">
         <f t="shared" si="10"/>
         <v>1.2158310624754842</v>
       </c>
@@ -3301,7 +3379,7 @@
         <f t="shared" si="9"/>
         <v>76.129203750396627</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="7">
         <f t="shared" si="10"/>
         <v>1.1624973812961878</v>
       </c>
@@ -3357,7 +3435,7 @@
         <f t="shared" si="9"/>
         <v>79.468689643272654</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="7">
         <f t="shared" si="10"/>
         <v>1.1136461466430116</v>
       </c>
@@ -3413,7 +3491,7 @@
         <f t="shared" si="9"/>
         <v>82.808175536148681</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="7">
         <f t="shared" si="10"/>
         <v>1.0687350545643484</v>
       </c>
@@ -3469,7 +3547,7 @@
         <f t="shared" si="9"/>
         <v>86.147661429024708</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="7">
         <f t="shared" si="10"/>
         <v>1.0273058900491843</v>
       </c>
@@ -3525,7 +3603,7 @@
         <f t="shared" si="9"/>
         <v>89.48714732190075</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="7">
         <f t="shared" si="10"/>
         <v>0.98896883685039361</v>
       </c>
@@ -3539,19 +3617,19 @@
         <v>660.4</v>
       </c>
       <c r="C35">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D35">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35">
         <f t="shared" si="2"/>
-        <v>85.5</v>
+        <v>87</v>
       </c>
       <c r="F35">
         <f t="shared" si="3"/>
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="G35">
         <f t="shared" si="11"/>
@@ -3567,23 +3645,23 @@
       </c>
       <c r="J35">
         <f t="shared" si="6"/>
-        <v>57</v>
+        <v>57.75</v>
       </c>
       <c r="K35" s="5">
         <f t="shared" si="7"/>
-        <v>2.4210526315789473</v>
+        <v>2.4736842105263159</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="8"/>
-        <v>86.826633214776791</v>
+        <v>84.979258039994278</v>
       </c>
       <c r="M35" s="5">
         <f t="shared" si="9"/>
-        <v>92.826633214776791</v>
-      </c>
-      <c r="N35" s="10">
+        <v>90.979258039994278</v>
+      </c>
+      <c r="N35" s="7">
         <f t="shared" si="10"/>
-        <v>0.95339017408111659</v>
+        <v>0.98923646926683229</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.4">
@@ -3595,19 +3673,19 @@
         <v>685.8</v>
       </c>
       <c r="C36">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D36">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E36">
         <f t="shared" si="2"/>
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="F36">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>91.5</v>
       </c>
       <c r="G36">
         <f t="shared" si="11"/>
@@ -3623,23 +3701,23 @@
       </c>
       <c r="J36">
         <f t="shared" si="6"/>
-        <v>57.75</v>
+        <v>58.5</v>
       </c>
       <c r="K36" s="5">
         <f t="shared" si="7"/>
-        <v>2.4736842105263159</v>
+        <v>2.5263157894736841</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="8"/>
-        <v>88.247691041532534</v>
+        <v>86.409197478167272</v>
       </c>
       <c r="M36" s="5">
         <f t="shared" si="9"/>
-        <v>94.247691041532534</v>
-      </c>
-      <c r="N36" s="10">
+        <v>92.409197478167272</v>
+      </c>
+      <c r="N36" s="7">
         <f t="shared" si="10"/>
-        <v>0.95493055591504428</v>
+        <v>0.99016117980699836</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.4">
@@ -3651,7 +3729,7 @@
         <v>711.19999999999993</v>
       </c>
       <c r="C37">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D37">
         <f t="shared" si="1"/>
@@ -3659,11 +3737,11 @@
       </c>
       <c r="E37">
         <f t="shared" si="2"/>
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="F37">
         <f t="shared" si="3"/>
-        <v>91.5</v>
+        <v>93</v>
       </c>
       <c r="G37">
         <f t="shared" si="11"/>
@@ -3679,7 +3757,7 @@
       </c>
       <c r="J37">
         <f t="shared" si="6"/>
-        <v>58.5</v>
+        <v>59.25</v>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="7"/>
@@ -3693,9 +3771,9 @@
         <f t="shared" si="9"/>
         <v>95.609538125506802</v>
       </c>
-      <c r="N37" s="10">
+      <c r="N37" s="7">
         <f t="shared" si="10"/>
-        <v>0.95701748794024921</v>
+        <v>0.97270629921795815</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.4">
@@ -3749,7 +3827,7 @@
         <f t="shared" si="9"/>
         <v>96.915799614216809</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="7">
         <f t="shared" si="10"/>
         <v>0.9750732117587313</v>
       </c>
@@ -3805,7 +3883,7 @@
         <f t="shared" si="9"/>
         <v>98.169810643378426</v>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="7">
         <f t="shared" si="10"/>
         <v>0.97789737365124707</v>
       </c>
@@ -3819,19 +3897,19 @@
         <v>787.4</v>
       </c>
       <c r="C40">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D40">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40">
         <f t="shared" si="2"/>
-        <v>93</v>
+        <v>94.5</v>
       </c>
       <c r="F40">
         <f t="shared" si="3"/>
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="G40">
         <f t="shared" si="11"/>
@@ -3847,23 +3925,23 @@
       </c>
       <c r="J40">
         <f t="shared" si="6"/>
-        <v>60.75</v>
+        <v>61.5</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" si="7"/>
-        <v>2.6315789473684212</v>
+        <v>2.6842105263157894</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="8"/>
-        <v>95.242137664824369</v>
+        <v>93.374644769435676</v>
       </c>
       <c r="M40" s="5">
         <f t="shared" si="9"/>
-        <v>101.24213766482437</v>
-      </c>
-      <c r="N40" s="10">
+        <v>99.374644769435676</v>
+      </c>
+      <c r="N40" s="7">
         <f t="shared" si="10"/>
-        <v>0.94822178012302383</v>
+        <v>0.98113558268524992</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.4">
@@ -3875,19 +3953,19 @@
         <v>812.8</v>
       </c>
       <c r="C41">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D41">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <f t="shared" si="2"/>
-        <v>94.5</v>
+        <v>96</v>
       </c>
       <c r="F41">
         <f t="shared" si="3"/>
-        <v>97.5</v>
+        <v>99</v>
       </c>
       <c r="G41">
         <f t="shared" si="11"/>
@@ -3903,23 +3981,23 @@
       </c>
       <c r="J41">
         <f t="shared" si="6"/>
-        <v>61.5</v>
+        <v>62.25</v>
       </c>
       <c r="K41" s="5">
         <f t="shared" si="7"/>
-        <v>2.6842105263157894</v>
+        <v>2.736842105263158</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="8"/>
-        <v>96.386730084578758</v>
+        <v>94.533139121413768</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="9"/>
-        <v>102.38673008457876</v>
-      </c>
-      <c r="N41" s="10">
+        <v>100.53313912141377</v>
+      </c>
+      <c r="N41" s="7">
         <f t="shared" si="10"/>
-        <v>0.95227184147260124</v>
+        <v>0.98474991296589076</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.4">
@@ -3931,7 +4009,7 @@
         <v>838.19999999999993</v>
       </c>
       <c r="C42">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D42">
         <f t="shared" si="1"/>
@@ -3939,11 +4017,11 @@
       </c>
       <c r="E42">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="F42">
         <f t="shared" si="3"/>
-        <v>99</v>
+        <v>100.5</v>
       </c>
       <c r="G42">
         <f t="shared" si="11"/>
@@ -3959,7 +4037,7 @@
       </c>
       <c r="J42">
         <f t="shared" si="6"/>
-        <v>62.25</v>
+        <v>63</v>
       </c>
       <c r="K42" s="5">
         <f t="shared" si="7"/>
@@ -3973,9 +4051,9 @@
         <f t="shared" si="9"/>
         <v>103.48729971895794</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="7">
         <f t="shared" si="10"/>
-        <v>0.9566391264324785</v>
+        <v>0.97113365865115242</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.4">
@@ -4029,7 +4107,7 @@
         <f t="shared" si="9"/>
         <v>104.54633842373795</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="7">
         <f t="shared" si="10"/>
         <v>0.97564392534325439</v>
       </c>
@@ -4043,19 +4121,19 @@
         <v>889</v>
       </c>
       <c r="C44">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D44">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E44">
         <f t="shared" si="2"/>
-        <v>99</v>
+        <v>100.5</v>
       </c>
       <c r="F44">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="G44">
         <f t="shared" si="11"/>
@@ -4071,23 +4149,23 @@
       </c>
       <c r="J44">
         <f t="shared" si="6"/>
-        <v>63.75</v>
+        <v>64.5</v>
       </c>
       <c r="K44" s="5">
         <f t="shared" si="7"/>
-        <v>2.7894736842105261</v>
+        <v>2.8421052631578947</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="8"/>
-        <v>101.44476014208318</v>
+        <v>99.566153472785345</v>
       </c>
       <c r="M44" s="5">
         <f t="shared" si="9"/>
-        <v>107.44476014208318</v>
-      </c>
-      <c r="N44" s="10">
+        <v>105.56615347278535</v>
+      </c>
+      <c r="N44" s="7">
         <f t="shared" si="10"/>
-        <v>0.94932502864836665</v>
+        <v>0.98042787953510124</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.4">
@@ -4099,19 +4177,19 @@
         <v>914.4</v>
       </c>
       <c r="C45">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D45">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E45">
         <f t="shared" si="2"/>
-        <v>100.5</v>
+        <v>102</v>
       </c>
       <c r="F45">
         <f t="shared" si="3"/>
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="G45">
         <f t="shared" si="11"/>
@@ -4127,23 +4205,23 @@
       </c>
       <c r="J45">
         <f t="shared" si="6"/>
-        <v>64.5</v>
+        <v>65.25</v>
       </c>
       <c r="K45" s="5">
         <f t="shared" si="7"/>
-        <v>2.8421052631578947</v>
+        <v>2.8947368421052633</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="8"/>
-        <v>102.41090071486492</v>
+        <v>100.54888433823102</v>
       </c>
       <c r="M45" s="5">
         <f t="shared" si="9"/>
-        <v>108.41090071486492</v>
-      </c>
-      <c r="N45" s="10">
+        <v>106.54888433823102</v>
+      </c>
+      <c r="N45" s="7">
         <f t="shared" si="10"/>
-        <v>0.95470104313789217</v>
+        <v>0.98546315761210401</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.4">
@@ -4155,19 +4233,19 @@
         <v>939.8</v>
       </c>
       <c r="C46">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D46">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <f t="shared" si="2"/>
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="F46">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="G46">
         <f t="shared" si="11"/>
@@ -4183,23 +4261,23 @@
       </c>
       <c r="J46">
         <f t="shared" si="6"/>
-        <v>65.25</v>
+        <v>66</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="7"/>
-        <v>2.8947368421052633</v>
+        <v>2.9473684210526314</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="8"/>
-        <v>103.34190890318186</v>
+        <v>101.49651767276791</v>
       </c>
       <c r="M46" s="5">
         <f t="shared" si="9"/>
-        <v>109.34190890318186</v>
-      </c>
-      <c r="N46" s="10">
+        <v>107.49651767276791</v>
+      </c>
+      <c r="N46" s="7">
         <f t="shared" si="10"/>
-        <v>0.96029053318406521</v>
+        <v>0.99072976786279321</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.4">
@@ -4211,7 +4289,7 @@
         <v>965.19999999999993</v>
       </c>
       <c r="C47">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D47">
         <f t="shared" si="1"/>
@@ -4219,11 +4297,11 @@
       </c>
       <c r="E47">
         <f t="shared" si="2"/>
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="F47">
         <f t="shared" si="3"/>
-        <v>106.5</v>
+        <v>108</v>
       </c>
       <c r="G47">
         <f t="shared" si="11"/>
@@ -4239,7 +4317,7 @@
       </c>
       <c r="J47">
         <f t="shared" si="6"/>
-        <v>66</v>
+        <v>66.75</v>
       </c>
       <c r="K47" s="5">
         <f t="shared" si="7"/>
@@ -4253,9 +4331,9 @@
         <f t="shared" si="9"/>
         <v>110.23966679905892</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="7">
         <f t="shared" si="10"/>
-        <v>0.96607694029159707</v>
+        <v>0.97968365776049282</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.4">
@@ -4267,19 +4345,19 @@
         <v>990.59999999999991</v>
       </c>
       <c r="C48">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D48">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E48">
         <f t="shared" si="2"/>
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="F48">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="G48">
         <f t="shared" si="11"/>
@@ -4295,23 +4373,23 @@
       </c>
       <c r="J48">
         <f t="shared" si="6"/>
-        <v>66.75</v>
+        <v>67.5</v>
       </c>
       <c r="K48" s="5">
         <f t="shared" si="7"/>
-        <v>2.9473684210526314</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5">
         <f t="shared" si="8"/>
-        <v>106.98281592534995</v>
+        <v>105.10592441788768</v>
       </c>
       <c r="M48" s="5">
         <f t="shared" si="9"/>
-        <v>112.98281592534995</v>
-      </c>
-      <c r="N48" s="10">
+        <v>111.10592441788768</v>
+      </c>
+      <c r="N48" s="7">
         <f t="shared" si="10"/>
-        <v>0.95589757712675349</v>
+        <v>0.98554600552309402</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.4">
@@ -4323,19 +4401,19 @@
         <v>1016</v>
       </c>
       <c r="C49">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49">
         <f t="shared" si="2"/>
-        <v>106.5</v>
+        <v>108</v>
       </c>
       <c r="F49">
         <f t="shared" si="3"/>
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="G49">
         <f t="shared" si="11"/>
@@ -4351,23 +4429,23 @@
       </c>
       <c r="J49">
         <f t="shared" si="6"/>
-        <v>67.5</v>
+        <v>68.25</v>
       </c>
       <c r="K49" s="5">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>3.0526315789473686</v>
       </c>
       <c r="L49" s="5">
         <f t="shared" si="8"/>
-        <v>107.80094812091045</v>
+        <v>105.94231108434302</v>
       </c>
       <c r="M49" s="5">
         <f t="shared" si="9"/>
-        <v>113.80094812091045</v>
-      </c>
-      <c r="N49" s="10">
+        <v>113.94231108434302</v>
+      </c>
+      <c r="N49" s="7">
         <f t="shared" si="10"/>
-        <v>0.96220639465726765</v>
+        <v>0.97417718618885096</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.4">
@@ -4421,7 +4499,7 @@
         <f t="shared" si="9"/>
         <v>114.75034566041005</v>
       </c>
-      <c r="N50" s="10">
+      <c r="N50" s="7">
         <f t="shared" si="10"/>
         <v>0.98038920364501836</v>
       </c>
@@ -4435,19 +4513,19 @@
         <v>1066.8</v>
       </c>
       <c r="C51">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D51">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51">
         <f t="shared" si="2"/>
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="F51">
         <f t="shared" si="3"/>
-        <v>112.5</v>
+        <v>114</v>
       </c>
       <c r="G51">
         <f t="shared" si="11"/>
@@ -4463,23 +4541,359 @@
       </c>
       <c r="J51">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>69.75</v>
       </c>
       <c r="K51" s="5">
         <f t="shared" si="7"/>
-        <v>3.1052631578947367</v>
+        <v>3.1578947368421053</v>
       </c>
       <c r="L51" s="5">
         <f t="shared" si="8"/>
-        <v>109.35401262773713</v>
+        <v>107.53144575060817</v>
       </c>
       <c r="M51" s="5">
         <f t="shared" si="9"/>
-        <v>117.35401262773713</v>
-      </c>
-      <c r="N51" s="10">
+        <v>115.53144575060817</v>
+      </c>
+      <c r="N51" s="7">
         <f t="shared" si="10"/>
-        <v>0.95863786402315254</v>
+        <v>0.98674433838632969</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>43</v>
+      </c>
+      <c r="B52">
+        <f t="shared" ref="B52" si="12">A52*25.4</f>
+        <v>1092.2</v>
+      </c>
+      <c r="C52">
+        <v>75</v>
+      </c>
+      <c r="D52">
+        <f t="shared" ref="D52" si="13">_xlfn.CEILING.MATH(0.8*C52)</f>
+        <v>60</v>
+      </c>
+      <c r="E52">
+        <f t="shared" ref="E52" si="14">C52*$C$1</f>
+        <v>112.5</v>
+      </c>
+      <c r="F52">
+        <f t="shared" ref="F52" si="15">E52+2*$C$1</f>
+        <v>115.5</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H52">
+        <f t="shared" ref="H52" si="16">G52*$C$1</f>
+        <v>28.5</v>
+      </c>
+      <c r="I52">
+        <f t="shared" ref="I52" si="17">H52+2*$C$1</f>
+        <v>31.5</v>
+      </c>
+      <c r="J52">
+        <f t="shared" ref="J52" si="18">(E52+H52)/2</f>
+        <v>70.5</v>
+      </c>
+      <c r="K52" s="5">
+        <f t="shared" ref="K52" si="19">D52/G52</f>
+        <v>3.1578947368421053</v>
+      </c>
+      <c r="L52" s="5">
+        <f t="shared" ref="L52" si="20">B52/K52/PI()</f>
+        <v>110.0917182684798</v>
+      </c>
+      <c r="M52" s="5">
+        <f t="shared" ref="M52" si="21">L52 + 4*$C$6*_xlfn.CEILING.MATH(K52)</f>
+        <v>118.0917182684798</v>
+      </c>
+      <c r="N52" s="7">
+        <f t="shared" ref="N52" si="22">F52/M52</f>
+        <v>0.97805334441330116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>44</v>
+      </c>
+      <c r="B53">
+        <f t="shared" ref="B53:B57" si="23">A53*25.4</f>
+        <v>1117.5999999999999</v>
+      </c>
+      <c r="C53">
+        <v>76</v>
+      </c>
+      <c r="D53">
+        <f t="shared" ref="D53:D57" si="24">_xlfn.CEILING.MATH(0.8*C53)</f>
+        <v>61</v>
+      </c>
+      <c r="E53">
+        <f t="shared" ref="E53:E57" si="25">C53*$C$1</f>
+        <v>114</v>
+      </c>
+      <c r="F53">
+        <f t="shared" ref="F53:F57" si="26">E53+2*$C$1</f>
+        <v>117</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H53">
+        <f t="shared" ref="H53:H57" si="27">G53*$C$1</f>
+        <v>28.5</v>
+      </c>
+      <c r="I53">
+        <f t="shared" ref="I53:I57" si="28">H53+2*$C$1</f>
+        <v>31.5</v>
+      </c>
+      <c r="J53">
+        <f t="shared" ref="J53:J57" si="29">(E53+H53)/2</f>
+        <v>71.25</v>
+      </c>
+      <c r="K53" s="5">
+        <f t="shared" ref="K53:K57" si="30">D53/G53</f>
+        <v>3.2105263157894739</v>
+      </c>
+      <c r="L53" s="5">
+        <f t="shared" ref="L53:L57" si="31">B53/K53/PI()</f>
+        <v>110.80523683903417</v>
+      </c>
+      <c r="M53" s="5">
+        <f t="shared" ref="M53:M57" si="32">L53 + 4*$C$6*_xlfn.CEILING.MATH(K53)</f>
+        <v>118.80523683903417</v>
+      </c>
+      <c r="N53" s="7">
+        <f t="shared" ref="N53:N57" si="33">F53/M53</f>
+        <v>0.98480507352146418</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>45</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="23"/>
+        <v>1143</v>
+      </c>
+      <c r="C54">
+        <v>77</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="24"/>
+        <v>62</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="25"/>
+        <v>115.5</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="26"/>
+        <v>118.5</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="27"/>
+        <v>28.5</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="28"/>
+        <v>31.5</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="29"/>
+        <v>72</v>
+      </c>
+      <c r="K54" s="5">
+        <f t="shared" si="30"/>
+        <v>3.263157894736842</v>
+      </c>
+      <c r="L54" s="5">
+        <f t="shared" si="31"/>
+        <v>111.49573868150618</v>
+      </c>
+      <c r="M54" s="5">
+        <f t="shared" si="32"/>
+        <v>119.49573868150618</v>
+      </c>
+      <c r="N54" s="7">
+        <f t="shared" si="33"/>
+        <v>0.99166716158673962</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>46</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="23"/>
+        <v>1168.3999999999999</v>
+      </c>
+      <c r="C55">
+        <v>77</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="24"/>
+        <v>62</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="25"/>
+        <v>115.5</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="26"/>
+        <v>118.5</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="27"/>
+        <v>28.5</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="28"/>
+        <v>31.5</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="29"/>
+        <v>72</v>
+      </c>
+      <c r="K55" s="5">
+        <f t="shared" si="30"/>
+        <v>3.263157894736842</v>
+      </c>
+      <c r="L55" s="5">
+        <f t="shared" si="31"/>
+        <v>113.9734217633174</v>
+      </c>
+      <c r="M55" s="5">
+        <f t="shared" si="32"/>
+        <v>121.9734217633174</v>
+      </c>
+      <c r="N55" s="7">
+        <f t="shared" si="33"/>
+        <v>0.97152312599660129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>47</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="23"/>
+        <v>1193.8</v>
+      </c>
+      <c r="C56">
+        <v>78</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="24"/>
+        <v>63</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="25"/>
+        <v>117</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="26"/>
+        <v>120</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="27"/>
+        <v>28.5</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="28"/>
+        <v>31.5</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="29"/>
+        <v>72.75</v>
+      </c>
+      <c r="K56" s="5">
+        <f t="shared" si="30"/>
+        <v>3.3157894736842106</v>
+      </c>
+      <c r="L56" s="5">
+        <f t="shared" si="31"/>
+        <v>114.6026746094917</v>
+      </c>
+      <c r="M56" s="5">
+        <f t="shared" si="32"/>
+        <v>122.6026746094917</v>
+      </c>
+      <c r="N56" s="7">
+        <f t="shared" si="33"/>
+        <v>0.9787714695639258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>48</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="23"/>
+        <v>1219.1999999999998</v>
+      </c>
+      <c r="C57">
+        <v>79</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="24"/>
+        <v>64</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="25"/>
+        <v>118.5</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="26"/>
+        <v>121.5</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="27"/>
+        <v>28.5</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="28"/>
+        <v>31.5</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="29"/>
+        <v>73.5</v>
+      </c>
+      <c r="K57" s="5">
+        <f t="shared" si="30"/>
+        <v>3.3684210526315788</v>
+      </c>
+      <c r="L57" s="5">
+        <f t="shared" si="31"/>
+        <v>115.21226330422303</v>
+      </c>
+      <c r="M57" s="5">
+        <f t="shared" si="32"/>
+        <v>123.21226330422303</v>
+      </c>
+      <c r="N57" s="7">
+        <f t="shared" si="33"/>
+        <v>0.98610314218483852</v>
       </c>
     </row>
   </sheetData>
@@ -4489,17 +4903,17 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="L8:M8"/>
   </mergeCells>
-  <conditionalFormatting sqref="I10:I51">
+  <conditionalFormatting sqref="I10:I57">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>M10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10:L51">
+  <conditionalFormatting sqref="L10:L57">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>$C$4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10:M51">
+  <conditionalFormatting sqref="M10:M57">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>2*J10 - $C$5</formula>
     </cfRule>
